--- a/samples/outputs/BRDAD010458440_NoCalculation_parsed.xlsx
+++ b/samples/outputs/BRDAD010458440_NoCalculation_parsed.xlsx
@@ -966,7 +966,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:27">
@@ -986,7 +986,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:27">
@@ -1006,7 +1006,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:27">
@@ -1026,7 +1026,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:27">
@@ -1046,7 +1046,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:27">
@@ -1066,7 +1066,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:27">
@@ -1086,7 +1086,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:27">
@@ -1106,7 +1106,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:27">
@@ -1126,7 +1126,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:27">
@@ -1146,7 +1146,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:27">
@@ -1166,7 +1166,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:27">
@@ -1186,7 +1186,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:27">
@@ -1206,7 +1206,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:27">
@@ -1226,7 +1226,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:27">
@@ -1246,7 +1246,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:27">
@@ -1266,7 +1266,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:27">
@@ -1286,7 +1286,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:27">
@@ -1306,7 +1306,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:27">
@@ -1326,7 +1326,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:27">
@@ -1346,7 +1346,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:27">
@@ -1366,7 +1366,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:27">
@@ -1386,7 +1386,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:27">
@@ -1406,7 +1406,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:27">
@@ -1426,7 +1426,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:27">
@@ -1446,7 +1446,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:27">
@@ -1466,7 +1466,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:27">
@@ -1506,7 +1506,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:27">
@@ -1586,7 +1586,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:27">
@@ -1606,7 +1606,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:27">
@@ -1626,7 +1626,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:27">
@@ -1646,7 +1646,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:27">
@@ -1666,7 +1666,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:27">
@@ -1686,7 +1686,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:27">
@@ -1706,7 +1706,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:27">
@@ -1726,7 +1726,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:27">
@@ -1746,7 +1746,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:27">
@@ -1766,7 +1766,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:27">
@@ -1786,7 +1786,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:27">
@@ -1806,7 +1806,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:27">
@@ -1826,7 +1826,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:27">
@@ -1846,7 +1846,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:27">
@@ -1866,7 +1866,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:27">
@@ -1886,7 +1886,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:27">
@@ -1906,7 +1906,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:27">
@@ -1926,7 +1926,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:27">
@@ -1946,7 +1946,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:27">
@@ -1966,7 +1966,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:27">
@@ -1986,7 +1986,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:27">
@@ -2006,7 +2006,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:27">
@@ -2026,7 +2026,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:27">
@@ -2046,7 +2046,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:27">
@@ -2066,7 +2066,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:27">
@@ -2086,7 +2086,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:27">
@@ -2126,7 +2126,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:27">

--- a/samples/outputs/BRDAD010458440_NoCalculation_parsed.xlsx
+++ b/samples/outputs/BRDAD010458440_NoCalculation_parsed.xlsx
@@ -114,7 +114,7 @@
     <x:t>256GB ThinkSystem ST650 V3 3yr Base Warranty</x:t>
   </x:si>
   <x:si>
-    <x:t>1.01</x:t>
+    <x:t>2</x:t>
   </x:si>
   <x:si>
     <x:t>BNW0</x:t>
@@ -123,7 +123,7 @@
     <x:t>ThinkSystem ST650 V3 - 2.5" Chassis Base</x:t>
   </x:si>
   <x:si>
-    <x:t>1.02</x:t>
+    <x:t>3</x:t>
   </x:si>
   <x:si>
     <x:t>BFYE</x:t>
@@ -132,7 +132,7 @@
     <x:t>Operating mode selection for: "Efficiency - Favoring Performance Mode"</x:t>
   </x:si>
   <x:si>
-    <x:t>1.03</x:t>
+    <x:t>4</x:t>
   </x:si>
   <x:si>
     <x:t>BNW2</x:t>
@@ -141,7 +141,7 @@
     <x:t>ThinkSystem ST650 V3 System Board</x:t>
   </x:si>
   <x:si>
-    <x:t>1.04</x:t>
+    <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>BL0H</x:t>
@@ -150,7 +150,7 @@
     <x:t>Data Center Environment 25 Degree Celsius / 77 Degree Fahrenheit</x:t>
   </x:si>
   <x:si>
-    <x:t>1.05</x:t>
+    <x:t>6</x:t>
   </x:si>
   <x:si>
     <x:t>BYW4</x:t>
@@ -159,7 +159,7 @@
     <x:t>Intel Xeon Silver 4510 12C 150W 2.4GHz Processor</x:t>
   </x:si>
   <x:si>
-    <x:t>1.06</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>BNF9</x:t>
@@ -168,7 +168,7 @@
     <x:t>ThinkSystem 64GB TruDDR5 4800MHz (2Rx4) 10x4 RDIMM</x:t>
   </x:si>
   <x:si>
-    <x:t>1.07</x:t>
+    <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>5978</x:t>
@@ -177,7 +177,7 @@
     <x:t>Select Storage devices - configured RAID</x:t>
   </x:si>
   <x:si>
-    <x:t>1.08</x:t>
+    <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>B8NW</x:t>
@@ -186,7 +186,7 @@
     <x:t>ThinkSystem RAID 940-8i 8GB Flash PCIe Gen4 12Gb Adapter</x:t>
   </x:si>
   <x:si>
-    <x:t>1.09</x:t>
+    <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>B9XG</x:t>
@@ -195,7 +195,7 @@
     <x:t>Controller 1 HW RAID Array 1 RAID 10</x:t>
   </x:si>
   <x:si>
-    <x:t>1.10</x:t>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>CABV</x:t>
@@ -204,7 +204,7 @@
     <x:t>ThinkSystem 2.5" VA 1.92TB Read Intensive SAS 24Gb HS SSD</x:t>
   </x:si>
   <x:si>
-    <x:t>1.11</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>B8LU</x:t>
@@ -213,7 +213,7 @@
     <x:t>ThinkSystem 2U 8x2.5" SAS/SATA Backplane</x:t>
   </x:si>
   <x:si>
-    <x:t>1.12</x:t>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>BNFG</x:t>
@@ -222,7 +222,7 @@
     <x:t>ThinkSystem 750W 230V/115V Platinum Hot-Swap Gen2 Power Supply v3</x:t>
   </x:si>
   <x:si>
-    <x:t>1.13</x:t>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>6400</x:t>
@@ -231,7 +231,7 @@
     <x:t>2.8m, 13A/100-250V, C13 to C14 Jumper Cord</x:t>
   </x:si>
   <x:si>
-    <x:t>1.14</x:t>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>BA5T</x:t>
@@ -240,7 +240,7 @@
     <x:t>ThinkSystem ST650 V2 Performance Fan Kit</x:t>
   </x:si>
   <x:si>
-    <x:t>1.15</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>BPKR</x:t>
@@ -249,7 +249,7 @@
     <x:t>TPM 2.0</x:t>
   </x:si>
   <x:si>
-    <x:t>1.16</x:t>
+    <x:t>17</x:t>
   </x:si>
   <x:si>
     <x:t>C8WV</x:t>
@@ -258,7 +258,7 @@
     <x:t>ST650/ST658 V3 Laser service indicator</x:t>
   </x:si>
   <x:si>
-    <x:t>1.17</x:t>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>2302</x:t>
@@ -267,7 +267,7 @@
     <x:t>RAID Configuration</x:t>
   </x:si>
   <x:si>
-    <x:t>1.18</x:t>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>BNW3</x:t>
@@ -276,7 +276,7 @@
     <x:t>ThinkSystem ST650 V3 Power PADDLE w/ GPU connect</x:t>
   </x:si>
   <x:si>
-    <x:t>1.19</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>BRPJ</x:t>
@@ -285,7 +285,7 @@
     <x:t>XCC Platinum</x:t>
   </x:si>
   <x:si>
-    <x:t>1.20</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>BA12</x:t>
@@ -294,7 +294,7 @@
     <x:t>Controller 1 HW RAID Array 1 HDDs</x:t>
   </x:si>
   <x:si>
-    <x:t>1.21</x:t>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>BNWR</x:t>
@@ -303,7 +303,7 @@
     <x:t>ThinkSystem SR860 V3/ST650 V3 CPU Heatsink</x:t>
   </x:si>
   <x:si>
-    <x:t>1.22</x:t>
+    <x:t>23</x:t>
   </x:si>
   <x:si>
     <x:t>AVEN</x:t>
@@ -312,7 +312,7 @@
     <x:t>ThinkSystem 1x1 2.5" HDD Filler</x:t>
   </x:si>
   <x:si>
-    <x:t>1.23</x:t>
+    <x:t>24</x:t>
   </x:si>
   <x:si>
     <x:t>AVEQ</x:t>
@@ -321,7 +321,7 @@
     <x:t>ThinkSystem 8x1 2.5" HDD Filler</x:t>
   </x:si>
   <x:si>
-    <x:t>1.24</x:t>
+    <x:t>25</x:t>
   </x:si>
   <x:si>
     <x:t>AUNP</x:t>
@@ -330,7 +330,7 @@
     <x:t>ThinkSystem RAID 930/940 SuperCap</x:t>
   </x:si>
   <x:si>
-    <x:t>1.25</x:t>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>BP0L</x:t>
@@ -339,7 +339,7 @@
     <x:t>ThinkSystem ST650 V3 RoT Card w/o PFR</x:t>
   </x:si>
   <x:si>
-    <x:t>1.26</x:t>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>5374CM1</x:t>
@@ -348,7 +348,7 @@
     <x:t>software1 Configuration Instruction</x:t>
   </x:si>
   <x:si>
-    <x:t>2</x:t>
+    <x:t>28</x:t>
   </x:si>
   <x:si>
     <x:t>7S0XCTO5WW</x:t>
@@ -357,7 +357,7 @@
     <x:t>software2 XClarity Controller Platin-FOD</x:t>
   </x:si>
   <x:si>
-    <x:t>2.01</x:t>
+    <x:t>29</x:t>
   </x:si>
   <x:si>
     <x:t>SBCV</x:t>
@@ -366,7 +366,7 @@
     <x:t>Lenovo XClarity XCC2 Platinum Upgrade (FOD)</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
+    <x:t>30</x:t>
   </x:si>
   <x:si>
     <x:t>5PS7C00099</x:t>
@@ -375,7 +375,7 @@
     <x:t>5Yr KYD Add-On ST650 V3</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
+    <x:t>31</x:t>
   </x:si>
   <x:si>
     <x:t>5WS7C00090</x:t>
@@ -384,100 +384,100 @@
     <x:t>5Yr Premier 24x7 4Hr Resp ST650 V3</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
+    <x:t>32</x:t>
   </x:si>
   <x:si>
     <x:t>512GB ThinkSystem ST650 V3 3yr Base Warranty</x:t>
   </x:si>
   <x:si>
-    <x:t>5.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
+    <x:t>33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62</x:t>
   </x:si>
   <x:si>
     <x:t>*</x:t>
